--- a/artfynd/A 28452-2020 artfynd.xlsx
+++ b/artfynd/A 28452-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 28452-2020 artfynd.xlsx
+++ b/artfynd/A 28452-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4507,6 +4507,422 @@
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>114653913</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57888</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Malmberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>746226</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7467042</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2023-05-29</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2023-05-29</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Emmy Ransgart</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>114653934</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57888</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Malmberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>746271</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7466715</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2023-05-29</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2023-05-29</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Emmy Ransgart</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>114653713</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57597</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Malmberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>745985</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7467012</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2023-06-21</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2023-06-21</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Matilda Andrén</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>114653718</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57888</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Malmberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>746127</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7466958</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2023-06-21</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2023-06-21</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Matilda Andrén</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
